--- a/data/employees/EMP010/AST-EMP010-06.xlsx
+++ b/data/employees/EMP010/AST-EMP010-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills Matrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,215 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Skills Matrix - Skyler Chen (HR)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Skyler Chen | Role: Manager | Location: Hsinchu | Date: 2025-01-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp010 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>65</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp010 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>90</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Employee ID</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Department</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Skills</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Last Review Date</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Rating</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp010 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>65</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EMP006</t>
+          <t>EMP010</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Avery Wilson</t>
+          <t>Ast Emp010 06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>2026-W04</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Specialist</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Azure AI, Fabric</t>
-        </is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>68</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>4.2</v>
+          <t>Section 1: Customer escalation analysis. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EMP011</t>
+          <t>EMP010</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Alex Garcia</t>
+          <t>Ast Emp010 06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>2026-W05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Lead</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Synapse, TypeScript</t>
-        </is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>73</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>3.9</v>
+          <t>Section 1: Operational risk review. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EMP016</t>
+          <t>EMP010</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Avery Wilson</t>
+          <t>Ast Emp010 06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>2026-W06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Engineer</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Python, SQL</t>
-        </is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>70</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>4.5</v>
+          <t>Section 1: Customer escalation analysis. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EMP021</t>
+          <t>EMP010</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alex Garcia</t>
+          <t>Ast Emp010 06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>2026-W07</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>69</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp010 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>72</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp010 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>98</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp010 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>64</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp010 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>74</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp010 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>83</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp010 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>67</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp010 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>88</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp010 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>80</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp010 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>96</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp010 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>77</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp010 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>82</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp010 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>95</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp010 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>83</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp010 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>88</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp010 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>79</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp010 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>92</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp010 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>99</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ontology, MLOps</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>4</v>
+          <t>Section 1: Customer escalation analysis. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP010</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP010 contributes to ast emp010 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>